--- a/artfynd/A 60241-2023 artfynd.xlsx
+++ b/artfynd/A 60241-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113714460</v>
+        <v>113714467</v>
       </c>
       <c r="B2" t="n">
-        <v>90412</v>
+        <v>97398</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655333</v>
+        <v>655505</v>
       </c>
       <c r="R2" t="n">
-        <v>7033147</v>
+        <v>7033075</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>200 orkidéer ca</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113714465</v>
+        <v>113714455</v>
       </c>
       <c r="B3" t="n">
-        <v>90142</v>
+        <v>81944</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1205</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655490</v>
+        <v>655214</v>
       </c>
       <c r="R3" t="n">
-        <v>7033070</v>
+        <v>7033129</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113712240</v>
+        <v>113712244</v>
       </c>
       <c r="B4" t="n">
-        <v>79223</v>
+        <v>56826</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +904,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229497</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655561</v>
+        <v>655634</v>
       </c>
       <c r="R4" t="n">
-        <v>7033047</v>
+        <v>7033016</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -963,6 +968,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>En hane på födosök</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113712227</v>
+        <v>113712245</v>
       </c>
       <c r="B5" t="n">
-        <v>97398</v>
+        <v>79265</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1015,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655289</v>
+        <v>655683</v>
       </c>
       <c r="R5" t="n">
-        <v>7033162</v>
+        <v>7032960</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1073,7 +1083,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>50 orkidéer ca</t>
+          <t>På sälghögstube</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113714448</v>
+        <v>113712233</v>
       </c>
       <c r="B6" t="n">
-        <v>78201</v>
+        <v>90142</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,25 +1126,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655402</v>
+        <v>655490</v>
       </c>
       <c r="R6" t="n">
-        <v>7033004</v>
+        <v>7033070</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1180,11 +1190,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Riklig</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113714455</v>
+        <v>113714453</v>
       </c>
       <c r="B7" t="n">
-        <v>81944</v>
+        <v>56955</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,21 +1236,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>655214</v>
+        <v>655150</v>
       </c>
       <c r="R7" t="n">
-        <v>7033129</v>
+        <v>7033208</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1291,6 +1296,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ett par i sitt häckningsrevir och födosöksområde</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113714463</v>
+        <v>113714452</v>
       </c>
       <c r="B8" t="n">
-        <v>90131</v>
+        <v>90077</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,21 +1347,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>655431</v>
+        <v>655288</v>
       </c>
       <c r="R8" t="n">
-        <v>7033087</v>
+        <v>7033050</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1427,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113714478</v>
+        <v>113714447</v>
       </c>
       <c r="B9" t="n">
-        <v>90412</v>
+        <v>90131</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1443,21 +1453,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>655697</v>
+        <v>655408</v>
       </c>
       <c r="R9" t="n">
-        <v>7032900</v>
+        <v>7032957</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1533,10 +1543,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113712252</v>
+        <v>113714484</v>
       </c>
       <c r="B10" t="n">
-        <v>90131</v>
+        <v>90518</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,21 +1559,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1573,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>655735</v>
+        <v>655744</v>
       </c>
       <c r="R10" t="n">
-        <v>7032900</v>
+        <v>7032871</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1639,10 +1644,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113712234</v>
+        <v>113714450</v>
       </c>
       <c r="B11" t="n">
-        <v>90131</v>
+        <v>90518</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1655,21 +1660,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>655508</v>
+        <v>655338</v>
       </c>
       <c r="R11" t="n">
-        <v>7033069</v>
+        <v>7033023</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113712244</v>
+        <v>113712247</v>
       </c>
       <c r="B12" t="n">
-        <v>56826</v>
+        <v>90412</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1761,21 +1761,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>655634</v>
+        <v>655697</v>
       </c>
       <c r="R12" t="n">
-        <v>7033016</v>
+        <v>7032900</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1821,11 +1821,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>En hane på födosök</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1856,10 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113712241</v>
+        <v>113712242</v>
       </c>
       <c r="B13" t="n">
-        <v>79265</v>
+        <v>90131</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1872,21 +1867,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1896,10 +1891,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>655567</v>
+        <v>655598</v>
       </c>
       <c r="R13" t="n">
-        <v>7033045</v>
+        <v>7033035</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1932,11 +1927,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På gamla aspar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1967,7 +1957,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113712215</v>
+        <v>113712234</v>
       </c>
       <c r="B14" t="n">
         <v>90131</v>
@@ -2007,10 +1997,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>655408</v>
+        <v>655508</v>
       </c>
       <c r="R14" t="n">
-        <v>7032957</v>
+        <v>7033069</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2073,10 +2063,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113712226</v>
+        <v>113712238</v>
       </c>
       <c r="B15" t="n">
-        <v>90573</v>
+        <v>90131</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2085,25 +2075,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2113,10 +2103,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>655210</v>
+        <v>655543</v>
       </c>
       <c r="R15" t="n">
-        <v>7033162</v>
+        <v>7033064</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2179,10 +2169,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113712222</v>
+        <v>113712216</v>
       </c>
       <c r="B16" t="n">
-        <v>81944</v>
+        <v>78201</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2195,21 +2185,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2219,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>655276</v>
+        <v>655402</v>
       </c>
       <c r="R16" t="n">
-        <v>7033079</v>
+        <v>7033004</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2257,13 +2247,17 @@
           <t>2023-10-15</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Riklig</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2286,7 +2280,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113714473</v>
+        <v>113712252</v>
       </c>
       <c r="B17" t="n">
         <v>90131</v>
@@ -2326,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655598</v>
+        <v>655735</v>
       </c>
       <c r="R17" t="n">
-        <v>7033035</v>
+        <v>7032900</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2392,10 +2386,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113714452</v>
+        <v>113712249</v>
       </c>
       <c r="B18" t="n">
-        <v>90077</v>
+        <v>90131</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2408,21 +2402,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2432,10 +2426,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655288</v>
+        <v>655709</v>
       </c>
       <c r="R18" t="n">
-        <v>7033050</v>
+        <v>7032901</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2498,10 +2492,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113714453</v>
+        <v>113712229</v>
       </c>
       <c r="B19" t="n">
-        <v>56955</v>
+        <v>90573</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2510,25 +2504,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2538,10 +2532,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>655150</v>
+        <v>655330</v>
       </c>
       <c r="R19" t="n">
-        <v>7033208</v>
+        <v>7033148</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2574,11 +2568,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ett par i sitt häckningsrevir och födosöksområde</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2609,10 +2598,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113714468</v>
+        <v>113712214</v>
       </c>
       <c r="B20" t="n">
-        <v>81944</v>
+        <v>90573</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2621,25 +2610,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2649,10 +2638,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>655511</v>
+        <v>655420</v>
       </c>
       <c r="R20" t="n">
-        <v>7033085</v>
+        <v>7032948</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2715,10 +2704,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113712217</v>
+        <v>113714485</v>
       </c>
       <c r="B21" t="n">
-        <v>90412</v>
+        <v>90149</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2731,21 +2720,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2755,10 +2744,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>655373</v>
+        <v>655756</v>
       </c>
       <c r="R21" t="n">
-        <v>7033024</v>
+        <v>7032864</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2821,10 +2810,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113714444</v>
+        <v>113714457</v>
       </c>
       <c r="B22" t="n">
-        <v>79265</v>
+        <v>90573</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2833,25 +2822,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2861,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>655471</v>
+        <v>655210</v>
       </c>
       <c r="R22" t="n">
-        <v>7032880</v>
+        <v>7033162</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2897,11 +2886,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2932,10 +2916,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113714476</v>
+        <v>113714477</v>
       </c>
       <c r="B23" t="n">
-        <v>79265</v>
+        <v>97398</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2944,25 +2928,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2972,10 +2956,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>655683</v>
+        <v>655686</v>
       </c>
       <c r="R23" t="n">
-        <v>7032960</v>
+        <v>7032933</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3012,7 +2996,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På sälghögstube</t>
+          <t>50 orkidéer ca</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3043,10 +3027,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113714461</v>
+        <v>113714468</v>
       </c>
       <c r="B24" t="n">
-        <v>90573</v>
+        <v>81944</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3055,25 +3039,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3083,10 +3067,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>655330</v>
+        <v>655511</v>
       </c>
       <c r="R24" t="n">
-        <v>7033148</v>
+        <v>7033085</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3149,10 +3133,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113714470</v>
+        <v>113714481</v>
       </c>
       <c r="B25" t="n">
-        <v>97398</v>
+        <v>90142</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3161,25 +3145,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1205</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3189,10 +3173,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>655550</v>
+        <v>655742</v>
       </c>
       <c r="R25" t="n">
-        <v>7033068</v>
+        <v>7032893</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3225,11 +3209,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>60 orkidéer ca</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3260,10 +3239,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113712243</v>
+        <v>113714449</v>
       </c>
       <c r="B26" t="n">
-        <v>79265</v>
+        <v>90412</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3276,21 +3255,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3300,10 +3279,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>655606</v>
+        <v>655373</v>
       </c>
       <c r="R26" t="n">
-        <v>7033029</v>
+        <v>7033024</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3336,11 +3315,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På 200 åriga björkar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3371,10 +3345,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113712238</v>
+        <v>113712219</v>
       </c>
       <c r="B27" t="n">
-        <v>90131</v>
+        <v>90149</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3387,21 +3361,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3411,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>655543</v>
+        <v>655296</v>
       </c>
       <c r="R27" t="n">
-        <v>7033064</v>
+        <v>7033043</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3477,10 +3451,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113712219</v>
+        <v>113712251</v>
       </c>
       <c r="B28" t="n">
-        <v>90149</v>
+        <v>79265</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3493,21 +3467,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3517,10 +3491,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>655296</v>
+        <v>655742</v>
       </c>
       <c r="R28" t="n">
-        <v>7033043</v>
+        <v>7032893</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3553,6 +3527,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På en asphögstubbe</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3583,10 +3562,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113714481</v>
+        <v>113712213</v>
       </c>
       <c r="B29" t="n">
-        <v>90142</v>
+        <v>90095</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3599,21 +3578,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1205</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3623,10 +3602,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>655742</v>
+        <v>655446</v>
       </c>
       <c r="R29" t="n">
-        <v>7032893</v>
+        <v>7032922</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3689,10 +3668,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113714445</v>
+        <v>113714459</v>
       </c>
       <c r="B30" t="n">
-        <v>90095</v>
+        <v>97398</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3701,25 +3680,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3729,10 +3708,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>655446</v>
+        <v>655289</v>
       </c>
       <c r="R30" t="n">
-        <v>7032922</v>
+        <v>7033162</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3765,6 +3744,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>50 orkidéer ca</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3795,7 +3779,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113714479</v>
+        <v>113714442</v>
       </c>
       <c r="B31" t="n">
         <v>90131</v>
@@ -3835,10 +3819,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>655704</v>
+        <v>655477</v>
       </c>
       <c r="R31" t="n">
-        <v>7032901</v>
+        <v>7032872</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3901,10 +3885,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113712218</v>
+        <v>113712240</v>
       </c>
       <c r="B32" t="n">
-        <v>90518</v>
+        <v>79223</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3913,20 +3897,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6040186</v>
+        <v>229497</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3936,10 +3925,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>655338</v>
+        <v>655561</v>
       </c>
       <c r="R32" t="n">
-        <v>7033023</v>
+        <v>7033047</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4002,7 +3991,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113712251</v>
+        <v>113714474</v>
       </c>
       <c r="B33" t="n">
         <v>79265</v>
@@ -4042,10 +4031,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>655742</v>
+        <v>655606</v>
       </c>
       <c r="R33" t="n">
-        <v>7032893</v>
+        <v>7033029</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4082,7 +4071,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På en asphögstubbe</t>
+          <t>På 200 åriga björkar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4113,10 +4102,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113712253</v>
+        <v>113714456</v>
       </c>
       <c r="B34" t="n">
-        <v>90518</v>
+        <v>97398</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4125,20 +4114,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6040186</v>
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4148,10 +4142,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>655744</v>
+        <v>655214</v>
       </c>
       <c r="R34" t="n">
-        <v>7032871</v>
+        <v>7033152</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4184,6 +4178,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>30 orkidéer</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4214,10 +4213,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113712214</v>
+        <v>113712231</v>
       </c>
       <c r="B35" t="n">
-        <v>90573</v>
+        <v>90131</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4226,25 +4225,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4254,10 +4253,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>655420</v>
+        <v>655431</v>
       </c>
       <c r="R35" t="n">
-        <v>7032948</v>
+        <v>7033087</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4320,10 +4319,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113712225</v>
+        <v>113714454</v>
       </c>
       <c r="B36" t="n">
-        <v>97398</v>
+        <v>81944</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4332,25 +4331,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4360,10 +4359,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>655214</v>
+        <v>655276</v>
       </c>
       <c r="R36" t="n">
-        <v>7033152</v>
+        <v>7033079</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4398,17 +4397,13 @@
           <t>2023-10-15</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>30 orkidéer</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4431,10 +4426,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113714477</v>
+        <v>113714444</v>
       </c>
       <c r="B37" t="n">
-        <v>97398</v>
+        <v>79265</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4443,25 +4438,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4471,10 +4466,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>655686</v>
+        <v>655471</v>
       </c>
       <c r="R37" t="n">
-        <v>7032933</v>
+        <v>7032880</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4511,7 +4506,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>50 orkidéer ca</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4542,10 +4537,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113712254</v>
+        <v>113712239</v>
       </c>
       <c r="B38" t="n">
-        <v>90149</v>
+        <v>97398</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4554,25 +4549,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4582,10 +4577,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>655756</v>
+        <v>655550</v>
       </c>
       <c r="R38" t="n">
-        <v>7032864</v>
+        <v>7033068</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4618,6 +4613,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>60 orkidéer ca</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4648,7 +4648,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113712249</v>
+        <v>113714479</v>
       </c>
       <c r="B39" t="n">
         <v>90131</v>
@@ -4688,7 +4688,7 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>655709</v>
+        <v>655704</v>
       </c>
       <c r="R39" t="n">
         <v>7032901</v>
@@ -4754,10 +4754,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113714467</v>
+        <v>113714472</v>
       </c>
       <c r="B40" t="n">
-        <v>97398</v>
+        <v>79265</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4766,25 +4766,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4794,10 +4794,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>655505</v>
+        <v>655567</v>
       </c>
       <c r="R40" t="n">
-        <v>7033075</v>
+        <v>7033045</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>200 orkidéer ca</t>
+          <t>På gamla aspar</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4865,10 +4865,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113714442</v>
+        <v>113714460</v>
       </c>
       <c r="B41" t="n">
-        <v>90131</v>
+        <v>90412</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4881,21 +4881,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>655477</v>
+        <v>655333</v>
       </c>
       <c r="R41" t="n">
-        <v>7032872</v>
+        <v>7033147</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>

--- a/artfynd/A 60241-2023 artfynd.xlsx
+++ b/artfynd/A 60241-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113714467</v>
+        <v>113712238</v>
       </c>
       <c r="B2" t="n">
-        <v>97398</v>
+        <v>90135</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655505</v>
+        <v>655543</v>
       </c>
       <c r="R2" t="n">
-        <v>7033075</v>
+        <v>7033064</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>200 orkidéer ca</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113714455</v>
+        <v>113714480</v>
       </c>
       <c r="B3" t="n">
-        <v>81944</v>
+        <v>90135</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655214</v>
+        <v>655709</v>
       </c>
       <c r="R3" t="n">
-        <v>7033129</v>
+        <v>7032901</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -892,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113712244</v>
+        <v>113714476</v>
       </c>
       <c r="B4" t="n">
-        <v>56826</v>
+        <v>79265</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655634</v>
+        <v>655683</v>
       </c>
       <c r="R4" t="n">
-        <v>7033016</v>
+        <v>7032960</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -972,7 +967,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>En hane på födosök</t>
+          <t>På sälghögstube</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113712245</v>
+        <v>113714447</v>
       </c>
       <c r="B5" t="n">
-        <v>79265</v>
+        <v>90135</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,21 +1014,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1043,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655683</v>
+        <v>655408</v>
       </c>
       <c r="R5" t="n">
-        <v>7032960</v>
+        <v>7032957</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1079,11 +1074,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På sälghögstube</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113712233</v>
+        <v>113712221</v>
       </c>
       <c r="B6" t="n">
-        <v>90142</v>
+        <v>56955</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,25 +1116,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1205</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1154,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655490</v>
+        <v>655150</v>
       </c>
       <c r="R6" t="n">
-        <v>7033070</v>
+        <v>7033208</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1190,6 +1180,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ett par i sitt häckningsrevir och födosöksområde</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113714453</v>
+        <v>113714445</v>
       </c>
       <c r="B7" t="n">
-        <v>56955</v>
+        <v>90099</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1232,25 +1227,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1260,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>655150</v>
+        <v>655446</v>
       </c>
       <c r="R7" t="n">
-        <v>7033208</v>
+        <v>7032922</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1296,11 +1291,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ett par i sitt häckningsrevir och födosöksområde</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1331,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113714452</v>
+        <v>113714477</v>
       </c>
       <c r="B8" t="n">
-        <v>90077</v>
+        <v>97402</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,25 +1333,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>655288</v>
+        <v>655686</v>
       </c>
       <c r="R8" t="n">
-        <v>7033050</v>
+        <v>7032933</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1407,6 +1397,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>50 orkidéer ca</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,10 +1432,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113714447</v>
+        <v>113714459</v>
       </c>
       <c r="B9" t="n">
-        <v>90131</v>
+        <v>97402</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,25 +1444,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1477,10 +1472,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>655408</v>
+        <v>655289</v>
       </c>
       <c r="R9" t="n">
-        <v>7032957</v>
+        <v>7033162</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1513,6 +1508,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>50 orkidéer ca</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1543,10 +1543,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113714484</v>
+        <v>113714468</v>
       </c>
       <c r="B10" t="n">
-        <v>90518</v>
+        <v>81944</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1559,16 +1559,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6040186</v>
+        <v>1312</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1578,10 +1583,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>655744</v>
+        <v>655511</v>
       </c>
       <c r="R10" t="n">
-        <v>7032871</v>
+        <v>7033085</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1644,10 +1649,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113714450</v>
+        <v>113712250</v>
       </c>
       <c r="B11" t="n">
-        <v>90518</v>
+        <v>90146</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1656,20 +1661,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6040186</v>
+        <v>1205</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Stor aspticka</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1689,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>655338</v>
+        <v>655742</v>
       </c>
       <c r="R11" t="n">
-        <v>7033023</v>
+        <v>7032893</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1745,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113712247</v>
+        <v>113714465</v>
       </c>
       <c r="B12" t="n">
-        <v>90412</v>
+        <v>90146</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1757,25 +1767,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>1205</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>655697</v>
+        <v>655490</v>
       </c>
       <c r="R12" t="n">
-        <v>7032900</v>
+        <v>7033070</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1851,10 +1861,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113712242</v>
+        <v>113714466</v>
       </c>
       <c r="B13" t="n">
-        <v>90131</v>
+        <v>90135</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1891,10 +1901,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>655598</v>
+        <v>655508</v>
       </c>
       <c r="R13" t="n">
-        <v>7033035</v>
+        <v>7033069</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1957,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113712234</v>
+        <v>113712252</v>
       </c>
       <c r="B14" t="n">
-        <v>90131</v>
+        <v>90135</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1997,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>655508</v>
+        <v>655735</v>
       </c>
       <c r="R14" t="n">
-        <v>7033069</v>
+        <v>7032900</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2063,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113712238</v>
+        <v>113714463</v>
       </c>
       <c r="B15" t="n">
-        <v>90131</v>
+        <v>90135</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2103,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>655543</v>
+        <v>655431</v>
       </c>
       <c r="R15" t="n">
-        <v>7033064</v>
+        <v>7033087</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2169,10 +2179,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113712216</v>
+        <v>113712240</v>
       </c>
       <c r="B16" t="n">
-        <v>78201</v>
+        <v>79223</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2181,25 +2191,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2209,10 +2219,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>655402</v>
+        <v>655561</v>
       </c>
       <c r="R16" t="n">
-        <v>7033004</v>
+        <v>7033047</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2245,11 +2255,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Riklig</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,10 +2285,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113712252</v>
+        <v>113714446</v>
       </c>
       <c r="B17" t="n">
-        <v>90131</v>
+        <v>90577</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2292,25 +2297,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2320,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655735</v>
+        <v>655420</v>
       </c>
       <c r="R17" t="n">
-        <v>7032900</v>
+        <v>7032948</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2386,10 +2391,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113712249</v>
+        <v>113712242</v>
       </c>
       <c r="B18" t="n">
-        <v>90131</v>
+        <v>90135</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2426,10 +2431,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655709</v>
+        <v>655598</v>
       </c>
       <c r="R18" t="n">
-        <v>7032901</v>
+        <v>7033035</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2492,10 +2497,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113712229</v>
+        <v>113714452</v>
       </c>
       <c r="B19" t="n">
-        <v>90573</v>
+        <v>90081</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2504,25 +2509,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>112</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2532,10 +2537,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>655330</v>
+        <v>655288</v>
       </c>
       <c r="R19" t="n">
-        <v>7033148</v>
+        <v>7033050</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2598,10 +2603,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113712214</v>
+        <v>113714448</v>
       </c>
       <c r="B20" t="n">
-        <v>90573</v>
+        <v>78201</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2610,25 +2615,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2638,10 +2643,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>655420</v>
+        <v>655402</v>
       </c>
       <c r="R20" t="n">
-        <v>7032948</v>
+        <v>7033004</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2674,6 +2679,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Riklig</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2704,10 +2714,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113714485</v>
+        <v>113712241</v>
       </c>
       <c r="B21" t="n">
-        <v>90149</v>
+        <v>79265</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2720,21 +2730,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2744,10 +2754,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>655756</v>
+        <v>655567</v>
       </c>
       <c r="R21" t="n">
-        <v>7032864</v>
+        <v>7033045</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2780,6 +2790,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På gamla aspar</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2810,10 +2825,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113714457</v>
+        <v>113714484</v>
       </c>
       <c r="B22" t="n">
-        <v>90573</v>
+        <v>90522</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2822,25 +2837,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,10 +2860,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>655210</v>
+        <v>655744</v>
       </c>
       <c r="R22" t="n">
-        <v>7033162</v>
+        <v>7032871</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2916,10 +2926,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113714477</v>
+        <v>113714450</v>
       </c>
       <c r="B23" t="n">
-        <v>97398</v>
+        <v>90522</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2928,25 +2938,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2956,10 +2961,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>655686</v>
+        <v>655338</v>
       </c>
       <c r="R23" t="n">
-        <v>7032933</v>
+        <v>7033023</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2992,11 +2997,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>50 orkidéer ca</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3027,10 +3027,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113714468</v>
+        <v>113714482</v>
       </c>
       <c r="B24" t="n">
-        <v>81944</v>
+        <v>79265</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3043,21 +3043,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>655511</v>
+        <v>655742</v>
       </c>
       <c r="R24" t="n">
-        <v>7033085</v>
+        <v>7032893</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3103,6 +3103,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På en asphögstubbe</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3133,10 +3138,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113714481</v>
+        <v>113712239</v>
       </c>
       <c r="B25" t="n">
-        <v>90142</v>
+        <v>97402</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3145,25 +3150,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1205</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3173,10 +3178,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>655742</v>
+        <v>655550</v>
       </c>
       <c r="R25" t="n">
-        <v>7032893</v>
+        <v>7033068</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3209,6 +3214,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>60 orkidéer ca</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3239,10 +3249,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113714449</v>
+        <v>113714455</v>
       </c>
       <c r="B26" t="n">
-        <v>90412</v>
+        <v>81944</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3255,21 +3265,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3279,10 +3289,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>655373</v>
+        <v>655214</v>
       </c>
       <c r="R26" t="n">
-        <v>7033024</v>
+        <v>7033129</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3345,10 +3355,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113712219</v>
+        <v>113714460</v>
       </c>
       <c r="B27" t="n">
-        <v>90149</v>
+        <v>90416</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3361,21 +3371,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3385,10 +3395,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>655296</v>
+        <v>655333</v>
       </c>
       <c r="R27" t="n">
-        <v>7033043</v>
+        <v>7033147</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3451,10 +3461,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113712251</v>
+        <v>113714449</v>
       </c>
       <c r="B28" t="n">
-        <v>79265</v>
+        <v>90416</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3467,21 +3477,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3491,10 +3501,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>655742</v>
+        <v>655373</v>
       </c>
       <c r="R28" t="n">
-        <v>7032893</v>
+        <v>7033024</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3527,11 +3537,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På en asphögstubbe</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3562,10 +3567,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113712213</v>
+        <v>113714475</v>
       </c>
       <c r="B29" t="n">
-        <v>90095</v>
+        <v>56826</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3574,25 +3579,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3602,10 +3607,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>655446</v>
+        <v>655634</v>
       </c>
       <c r="R29" t="n">
-        <v>7032922</v>
+        <v>7033016</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3638,6 +3643,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>En hane på födosök</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3668,10 +3678,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113714459</v>
+        <v>113712229</v>
       </c>
       <c r="B30" t="n">
-        <v>97398</v>
+        <v>90577</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3684,21 +3694,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3708,10 +3718,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>655289</v>
+        <v>655330</v>
       </c>
       <c r="R30" t="n">
-        <v>7033162</v>
+        <v>7033148</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3744,11 +3754,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>50 orkidéer ca</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3779,10 +3784,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113714442</v>
+        <v>113712235</v>
       </c>
       <c r="B31" t="n">
-        <v>90131</v>
+        <v>97402</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3791,25 +3796,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3819,10 +3824,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>655477</v>
+        <v>655505</v>
       </c>
       <c r="R31" t="n">
-        <v>7032872</v>
+        <v>7033075</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3855,6 +3860,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>200 orkidéer ca</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3885,10 +3895,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113712240</v>
+        <v>113714457</v>
       </c>
       <c r="B32" t="n">
-        <v>79223</v>
+        <v>90577</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3897,25 +3907,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229497</v>
+        <v>1209</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3925,10 +3935,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>655561</v>
+        <v>655210</v>
       </c>
       <c r="R32" t="n">
-        <v>7033047</v>
+        <v>7033162</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3991,10 +4001,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113714474</v>
+        <v>113712248</v>
       </c>
       <c r="B33" t="n">
-        <v>79265</v>
+        <v>90135</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4007,21 +4017,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4031,10 +4041,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>655606</v>
+        <v>655704</v>
       </c>
       <c r="R33" t="n">
-        <v>7033029</v>
+        <v>7032901</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4067,11 +4077,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På 200 åriga björkar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4102,10 +4107,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113714456</v>
+        <v>113714442</v>
       </c>
       <c r="B34" t="n">
-        <v>97398</v>
+        <v>90135</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4114,25 +4119,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4142,10 +4147,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>655214</v>
+        <v>655477</v>
       </c>
       <c r="R34" t="n">
-        <v>7033152</v>
+        <v>7032872</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4178,11 +4183,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>30 orkidéer</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4213,10 +4213,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113712231</v>
+        <v>113714485</v>
       </c>
       <c r="B35" t="n">
-        <v>90131</v>
+        <v>90153</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4229,21 +4229,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4253,10 +4253,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>655431</v>
+        <v>655756</v>
       </c>
       <c r="R35" t="n">
-        <v>7033087</v>
+        <v>7032864</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4319,10 +4319,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113714454</v>
+        <v>113712247</v>
       </c>
       <c r="B36" t="n">
-        <v>81944</v>
+        <v>90416</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4335,21 +4335,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4359,10 +4359,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>655276</v>
+        <v>655697</v>
       </c>
       <c r="R36" t="n">
-        <v>7033079</v>
+        <v>7032900</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4403,7 +4403,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4426,10 +4425,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113714444</v>
+        <v>113712222</v>
       </c>
       <c r="B37" t="n">
-        <v>79265</v>
+        <v>81944</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4442,21 +4441,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4466,10 +4465,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>655471</v>
+        <v>655276</v>
       </c>
       <c r="R37" t="n">
-        <v>7032880</v>
+        <v>7033079</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4504,17 +4503,13 @@
           <t>2023-10-15</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4537,10 +4532,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113712239</v>
+        <v>113714456</v>
       </c>
       <c r="B38" t="n">
-        <v>97398</v>
+        <v>97402</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4577,10 +4572,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>655550</v>
+        <v>655214</v>
       </c>
       <c r="R38" t="n">
-        <v>7033068</v>
+        <v>7033152</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4617,7 +4612,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>60 orkidéer ca</t>
+          <t>30 orkidéer</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4648,10 +4643,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113714479</v>
+        <v>113712219</v>
       </c>
       <c r="B39" t="n">
-        <v>90131</v>
+        <v>90153</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4664,21 +4659,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4688,10 +4683,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>655704</v>
+        <v>655296</v>
       </c>
       <c r="R39" t="n">
-        <v>7032901</v>
+        <v>7033043</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4754,7 +4749,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113714472</v>
+        <v>113714474</v>
       </c>
       <c r="B40" t="n">
         <v>79265</v>
@@ -4794,10 +4789,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>655567</v>
+        <v>655606</v>
       </c>
       <c r="R40" t="n">
-        <v>7033045</v>
+        <v>7033029</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4834,7 +4829,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På gamla aspar</t>
+          <t>På 200 åriga björkar</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4865,10 +4860,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113714460</v>
+        <v>113714444</v>
       </c>
       <c r="B41" t="n">
-        <v>90412</v>
+        <v>79265</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4881,21 +4876,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4905,10 +4900,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>655333</v>
+        <v>655471</v>
       </c>
       <c r="R41" t="n">
-        <v>7033147</v>
+        <v>7032880</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4941,6 +4936,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 60241-2023 artfynd.xlsx
+++ b/artfynd/A 60241-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113712238</v>
+        <v>113714447</v>
       </c>
       <c r="B2" t="n">
         <v>90135</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655543</v>
+        <v>655408</v>
       </c>
       <c r="R2" t="n">
-        <v>7033064</v>
+        <v>7032957</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113714476</v>
+        <v>113714455</v>
       </c>
       <c r="B4" t="n">
-        <v>79265</v>
+        <v>81944</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655683</v>
+        <v>655214</v>
       </c>
       <c r="R4" t="n">
-        <v>7032960</v>
+        <v>7033129</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -963,11 +963,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På sälghögstube</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113714447</v>
+        <v>113712214</v>
       </c>
       <c r="B5" t="n">
-        <v>90135</v>
+        <v>90577</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655408</v>
+        <v>655420</v>
       </c>
       <c r="R5" t="n">
-        <v>7032957</v>
+        <v>7032948</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113712221</v>
+        <v>113714444</v>
       </c>
       <c r="B6" t="n">
-        <v>56955</v>
+        <v>79265</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655150</v>
+        <v>655471</v>
       </c>
       <c r="R6" t="n">
-        <v>7033208</v>
+        <v>7032880</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1184,7 +1179,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ett par i sitt häckningsrevir och födosöksområde</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113714445</v>
+        <v>113712228</v>
       </c>
       <c r="B7" t="n">
-        <v>90099</v>
+        <v>90416</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,25 +1222,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>655446</v>
+        <v>655333</v>
       </c>
       <c r="R7" t="n">
-        <v>7032922</v>
+        <v>7033147</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1321,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113714477</v>
+        <v>113714445</v>
       </c>
       <c r="B8" t="n">
-        <v>97402</v>
+        <v>90099</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,25 +1328,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>655686</v>
+        <v>655446</v>
       </c>
       <c r="R8" t="n">
-        <v>7032933</v>
+        <v>7032922</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1397,11 +1392,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>50 orkidéer ca</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113714459</v>
+        <v>113712217</v>
       </c>
       <c r="B9" t="n">
-        <v>97402</v>
+        <v>90416</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1444,25 +1434,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1472,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>655289</v>
+        <v>655373</v>
       </c>
       <c r="R9" t="n">
-        <v>7033162</v>
+        <v>7033024</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1508,11 +1498,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>50 orkidéer ca</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1543,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113714468</v>
+        <v>113714485</v>
       </c>
       <c r="B10" t="n">
-        <v>81944</v>
+        <v>90153</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1559,21 +1544,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1583,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>655511</v>
+        <v>655756</v>
       </c>
       <c r="R10" t="n">
-        <v>7033085</v>
+        <v>7032864</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1649,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113712250</v>
+        <v>113712244</v>
       </c>
       <c r="B11" t="n">
-        <v>90146</v>
+        <v>56826</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1661,25 +1646,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1205</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1689,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>655742</v>
+        <v>655634</v>
       </c>
       <c r="R11" t="n">
-        <v>7032893</v>
+        <v>7033016</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1725,6 +1710,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>En hane på födosök</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113714465</v>
+        <v>113712245</v>
       </c>
       <c r="B12" t="n">
-        <v>90146</v>
+        <v>79265</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1767,25 +1757,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1795,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>655490</v>
+        <v>655683</v>
       </c>
       <c r="R12" t="n">
-        <v>7033070</v>
+        <v>7032960</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1831,6 +1821,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På sälghögstube</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1861,10 +1856,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113714466</v>
+        <v>113714471</v>
       </c>
       <c r="B13" t="n">
-        <v>90135</v>
+        <v>79223</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1873,25 +1868,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1901,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>655508</v>
+        <v>655561</v>
       </c>
       <c r="R13" t="n">
-        <v>7033069</v>
+        <v>7033047</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1967,7 +1962,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113712252</v>
+        <v>113714463</v>
       </c>
       <c r="B14" t="n">
         <v>90135</v>
@@ -2007,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>655735</v>
+        <v>655431</v>
       </c>
       <c r="R14" t="n">
-        <v>7032900</v>
+        <v>7033087</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2073,10 +2068,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113714463</v>
+        <v>113712216</v>
       </c>
       <c r="B15" t="n">
-        <v>90135</v>
+        <v>78201</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2089,21 +2084,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2113,10 +2108,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>655431</v>
+        <v>655402</v>
       </c>
       <c r="R15" t="n">
-        <v>7033087</v>
+        <v>7033004</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2149,6 +2144,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Riklig</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2179,10 +2179,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113712240</v>
+        <v>113714470</v>
       </c>
       <c r="B16" t="n">
-        <v>79223</v>
+        <v>97402</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2191,25 +2191,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>655561</v>
+        <v>655550</v>
       </c>
       <c r="R16" t="n">
-        <v>7033047</v>
+        <v>7033068</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2255,6 +2255,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>60 orkidéer ca</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2285,7 +2290,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113714446</v>
+        <v>113714457</v>
       </c>
       <c r="B17" t="n">
         <v>90577</v>
@@ -2325,10 +2330,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655420</v>
+        <v>655210</v>
       </c>
       <c r="R17" t="n">
-        <v>7032948</v>
+        <v>7033162</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2391,7 +2396,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113712242</v>
+        <v>113712238</v>
       </c>
       <c r="B18" t="n">
         <v>90135</v>
@@ -2431,10 +2436,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655598</v>
+        <v>655543</v>
       </c>
       <c r="R18" t="n">
-        <v>7033035</v>
+        <v>7033064</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2497,10 +2502,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113714452</v>
+        <v>113712242</v>
       </c>
       <c r="B19" t="n">
-        <v>90081</v>
+        <v>90135</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2513,21 +2518,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2537,10 +2542,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>655288</v>
+        <v>655598</v>
       </c>
       <c r="R19" t="n">
-        <v>7033050</v>
+        <v>7033035</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2603,10 +2608,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113714448</v>
+        <v>113712237</v>
       </c>
       <c r="B20" t="n">
-        <v>78201</v>
+        <v>81944</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2619,21 +2624,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2643,10 +2648,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>655402</v>
+        <v>655511</v>
       </c>
       <c r="R20" t="n">
-        <v>7033004</v>
+        <v>7033085</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2679,11 +2684,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Riklig</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2714,10 +2714,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113712241</v>
+        <v>113714459</v>
       </c>
       <c r="B21" t="n">
-        <v>79265</v>
+        <v>97402</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2726,25 +2726,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>655567</v>
+        <v>655289</v>
       </c>
       <c r="R21" t="n">
-        <v>7033045</v>
+        <v>7033162</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gamla aspar</t>
+          <t>50 orkidéer ca</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2825,10 +2825,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113714484</v>
+        <v>113712235</v>
       </c>
       <c r="B22" t="n">
-        <v>90522</v>
+        <v>97402</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2837,20 +2837,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6040186</v>
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2860,10 +2865,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>655744</v>
+        <v>655505</v>
       </c>
       <c r="R22" t="n">
-        <v>7032871</v>
+        <v>7033075</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2896,6 +2901,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>200 orkidéer ca</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2926,10 +2936,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113714450</v>
+        <v>113712233</v>
       </c>
       <c r="B23" t="n">
-        <v>90522</v>
+        <v>90146</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2938,20 +2948,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6040186</v>
+        <v>1205</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Stor aspticka</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2961,10 +2976,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>655338</v>
+        <v>655490</v>
       </c>
       <c r="R23" t="n">
-        <v>7033023</v>
+        <v>7033070</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3027,7 +3042,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113714482</v>
+        <v>113712243</v>
       </c>
       <c r="B24" t="n">
         <v>79265</v>
@@ -3067,10 +3082,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>655742</v>
+        <v>655606</v>
       </c>
       <c r="R24" t="n">
-        <v>7032893</v>
+        <v>7033029</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3107,7 +3122,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På en asphögstubbe</t>
+          <t>På 200 åriga björkar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3138,10 +3153,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113712239</v>
+        <v>113714481</v>
       </c>
       <c r="B25" t="n">
-        <v>97402</v>
+        <v>90146</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3150,25 +3165,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1205</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3178,10 +3193,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>655550</v>
+        <v>655742</v>
       </c>
       <c r="R25" t="n">
-        <v>7033068</v>
+        <v>7032893</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3214,11 +3229,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>60 orkidéer ca</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3249,10 +3259,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113714455</v>
+        <v>113714477</v>
       </c>
       <c r="B26" t="n">
-        <v>81944</v>
+        <v>97402</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3261,25 +3271,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3289,10 +3299,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>655214</v>
+        <v>655686</v>
       </c>
       <c r="R26" t="n">
-        <v>7033129</v>
+        <v>7032933</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3325,6 +3335,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>50 orkidéer ca</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3355,10 +3370,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113714460</v>
+        <v>113712241</v>
       </c>
       <c r="B27" t="n">
-        <v>90416</v>
+        <v>79265</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3371,21 +3386,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3395,10 +3410,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>655333</v>
+        <v>655567</v>
       </c>
       <c r="R27" t="n">
-        <v>7033147</v>
+        <v>7033045</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3431,6 +3446,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På gamla aspar</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3461,10 +3481,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113714449</v>
+        <v>113714482</v>
       </c>
       <c r="B28" t="n">
-        <v>90416</v>
+        <v>79265</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3477,21 +3497,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3501,10 +3521,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>655373</v>
+        <v>655742</v>
       </c>
       <c r="R28" t="n">
-        <v>7033024</v>
+        <v>7032893</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3537,6 +3557,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På en asphögstubbe</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3567,10 +3592,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113714475</v>
+        <v>113712219</v>
       </c>
       <c r="B29" t="n">
-        <v>56826</v>
+        <v>90153</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3583,21 +3608,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3607,10 +3632,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>655634</v>
+        <v>655296</v>
       </c>
       <c r="R29" t="n">
-        <v>7033016</v>
+        <v>7033043</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3643,11 +3668,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>En hane på födosök</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3678,10 +3698,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113712229</v>
+        <v>113712252</v>
       </c>
       <c r="B30" t="n">
-        <v>90577</v>
+        <v>90135</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3690,25 +3710,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3718,10 +3738,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>655330</v>
+        <v>655735</v>
       </c>
       <c r="R30" t="n">
-        <v>7033148</v>
+        <v>7032900</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3784,10 +3804,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113712235</v>
+        <v>113712222</v>
       </c>
       <c r="B31" t="n">
-        <v>97402</v>
+        <v>81944</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3796,25 +3816,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3824,10 +3844,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>655505</v>
+        <v>655276</v>
       </c>
       <c r="R31" t="n">
-        <v>7033075</v>
+        <v>7033079</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3862,17 +3882,13 @@
           <t>2023-10-15</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>200 orkidéer ca</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3895,10 +3911,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113714457</v>
+        <v>113712248</v>
       </c>
       <c r="B32" t="n">
-        <v>90577</v>
+        <v>90135</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3907,25 +3923,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3935,10 +3951,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>655210</v>
+        <v>655704</v>
       </c>
       <c r="R32" t="n">
-        <v>7033162</v>
+        <v>7032901</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4001,10 +4017,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113712248</v>
+        <v>113712221</v>
       </c>
       <c r="B33" t="n">
-        <v>90135</v>
+        <v>56955</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4017,21 +4033,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4041,10 +4057,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>655704</v>
+        <v>655150</v>
       </c>
       <c r="R33" t="n">
-        <v>7032901</v>
+        <v>7033208</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4077,6 +4093,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ett par i sitt häckningsrevir och födosöksområde</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4107,10 +4128,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113714442</v>
+        <v>113714456</v>
       </c>
       <c r="B34" t="n">
-        <v>90135</v>
+        <v>97402</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4119,25 +4140,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4147,10 +4168,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>655477</v>
+        <v>655214</v>
       </c>
       <c r="R34" t="n">
-        <v>7032872</v>
+        <v>7033152</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4183,6 +4204,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>30 orkidéer</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4213,10 +4239,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113714485</v>
+        <v>113712247</v>
       </c>
       <c r="B35" t="n">
-        <v>90153</v>
+        <v>90416</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4229,21 +4255,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4253,10 +4279,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>655756</v>
+        <v>655697</v>
       </c>
       <c r="R35" t="n">
-        <v>7032864</v>
+        <v>7032900</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4319,10 +4345,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113712247</v>
+        <v>113712218</v>
       </c>
       <c r="B36" t="n">
-        <v>90416</v>
+        <v>90522</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4335,21 +4361,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4359,10 +4380,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>655697</v>
+        <v>655338</v>
       </c>
       <c r="R36" t="n">
-        <v>7032900</v>
+        <v>7033023</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4425,10 +4446,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113712222</v>
+        <v>113712211</v>
       </c>
       <c r="B37" t="n">
-        <v>81944</v>
+        <v>90135</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4441,21 +4462,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4465,10 +4486,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>655276</v>
+        <v>655477</v>
       </c>
       <c r="R37" t="n">
-        <v>7033079</v>
+        <v>7032872</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4509,7 +4530,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4532,10 +4552,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113714456</v>
+        <v>113714484</v>
       </c>
       <c r="B38" t="n">
-        <v>97402</v>
+        <v>90522</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4544,25 +4564,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4572,10 +4587,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>655214</v>
+        <v>655744</v>
       </c>
       <c r="R38" t="n">
-        <v>7033152</v>
+        <v>7032871</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4608,11 +4623,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>30 orkidéer</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4643,10 +4653,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113712219</v>
+        <v>113712234</v>
       </c>
       <c r="B39" t="n">
-        <v>90153</v>
+        <v>90135</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4659,21 +4669,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4683,10 +4693,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>655296</v>
+        <v>655508</v>
       </c>
       <c r="R39" t="n">
-        <v>7033043</v>
+        <v>7033069</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4749,10 +4759,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113714474</v>
+        <v>113714461</v>
       </c>
       <c r="B40" t="n">
-        <v>79265</v>
+        <v>90577</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4761,25 +4771,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4789,10 +4799,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>655606</v>
+        <v>655330</v>
       </c>
       <c r="R40" t="n">
-        <v>7033029</v>
+        <v>7033148</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4825,11 +4835,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På 200 åriga björkar</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4860,10 +4865,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113714444</v>
+        <v>113712220</v>
       </c>
       <c r="B41" t="n">
-        <v>79265</v>
+        <v>90081</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4876,21 +4881,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4900,10 +4905,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>655471</v>
+        <v>655288</v>
       </c>
       <c r="R41" t="n">
-        <v>7032880</v>
+        <v>7033050</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4936,11 +4941,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 60241-2023 artfynd.xlsx
+++ b/artfynd/A 60241-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113714447</v>
+        <v>113714445</v>
       </c>
       <c r="B2" t="n">
-        <v>90135</v>
+        <v>90099</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655408</v>
+        <v>655446</v>
       </c>
       <c r="R2" t="n">
-        <v>7032957</v>
+        <v>7032922</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113714480</v>
+        <v>113712235</v>
       </c>
       <c r="B3" t="n">
-        <v>90135</v>
+        <v>97402</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655709</v>
+        <v>655505</v>
       </c>
       <c r="R3" t="n">
-        <v>7032901</v>
+        <v>7033075</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,6 +857,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>200 orkidéer ca</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113714455</v>
+        <v>113714450</v>
       </c>
       <c r="B4" t="n">
-        <v>81944</v>
+        <v>90522</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +908,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655214</v>
+        <v>655338</v>
       </c>
       <c r="R4" t="n">
-        <v>7033129</v>
+        <v>7033023</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113712214</v>
+        <v>113714442</v>
       </c>
       <c r="B5" t="n">
-        <v>90577</v>
+        <v>90135</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655420</v>
+        <v>655477</v>
       </c>
       <c r="R5" t="n">
-        <v>7032948</v>
+        <v>7032872</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113714444</v>
+        <v>113712237</v>
       </c>
       <c r="B6" t="n">
-        <v>79265</v>
+        <v>81944</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655471</v>
+        <v>655511</v>
       </c>
       <c r="R6" t="n">
-        <v>7032880</v>
+        <v>7033085</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1175,11 +1175,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113712228</v>
+        <v>113712241</v>
       </c>
       <c r="B7" t="n">
-        <v>90416</v>
+        <v>79265</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>655333</v>
+        <v>655567</v>
       </c>
       <c r="R7" t="n">
-        <v>7033147</v>
+        <v>7033045</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1286,6 +1281,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gamla aspar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113714445</v>
+        <v>113714482</v>
       </c>
       <c r="B8" t="n">
-        <v>90099</v>
+        <v>79265</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,25 +1328,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>655446</v>
+        <v>655742</v>
       </c>
       <c r="R8" t="n">
-        <v>7032922</v>
+        <v>7032893</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1392,6 +1392,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På en asphögstubbe</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,7 +1427,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113712217</v>
+        <v>113712247</v>
       </c>
       <c r="B9" t="n">
         <v>90416</v>
@@ -1462,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>655373</v>
+        <v>655697</v>
       </c>
       <c r="R9" t="n">
-        <v>7033024</v>
+        <v>7032900</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1528,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113714485</v>
+        <v>113712227</v>
       </c>
       <c r="B10" t="n">
-        <v>90153</v>
+        <v>97402</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,25 +1545,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>655756</v>
+        <v>655289</v>
       </c>
       <c r="R10" t="n">
-        <v>7032864</v>
+        <v>7033162</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1604,6 +1609,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>50 orkidéer ca</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1634,10 +1644,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113712244</v>
+        <v>113714465</v>
       </c>
       <c r="B11" t="n">
-        <v>56826</v>
+        <v>90146</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,25 +1656,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>1205</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>655634</v>
+        <v>655490</v>
       </c>
       <c r="R11" t="n">
-        <v>7033016</v>
+        <v>7033070</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1710,11 +1720,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>En hane på födosök</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113712245</v>
+        <v>113714460</v>
       </c>
       <c r="B12" t="n">
-        <v>79265</v>
+        <v>90416</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1761,21 +1766,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>655683</v>
+        <v>655333</v>
       </c>
       <c r="R12" t="n">
-        <v>7032960</v>
+        <v>7033147</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1821,11 +1826,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På sälghögstube</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1962,10 +1962,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113714463</v>
+        <v>113714485</v>
       </c>
       <c r="B14" t="n">
-        <v>90135</v>
+        <v>90153</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1978,21 +1978,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>655431</v>
+        <v>655756</v>
       </c>
       <c r="R14" t="n">
-        <v>7033087</v>
+        <v>7032864</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2068,10 +2068,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113712216</v>
+        <v>113712217</v>
       </c>
       <c r="B15" t="n">
-        <v>78201</v>
+        <v>90416</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2084,21 +2084,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>655402</v>
+        <v>655373</v>
       </c>
       <c r="R15" t="n">
-        <v>7033004</v>
+        <v>7033024</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2144,11 +2144,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Riklig</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2179,10 +2174,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113714470</v>
+        <v>113712242</v>
       </c>
       <c r="B16" t="n">
-        <v>97402</v>
+        <v>90135</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2191,25 +2186,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2219,10 +2214,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>655550</v>
+        <v>655598</v>
       </c>
       <c r="R16" t="n">
-        <v>7033068</v>
+        <v>7033035</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2255,11 +2250,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>60 orkidéer ca</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2290,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113714457</v>
+        <v>113712250</v>
       </c>
       <c r="B17" t="n">
-        <v>90577</v>
+        <v>90146</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2302,25 +2292,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>1205</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2330,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655210</v>
+        <v>655742</v>
       </c>
       <c r="R17" t="n">
-        <v>7033162</v>
+        <v>7032893</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2396,10 +2386,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113712238</v>
+        <v>113714475</v>
       </c>
       <c r="B18" t="n">
-        <v>90135</v>
+        <v>56826</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2412,21 +2402,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2436,10 +2426,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655543</v>
+        <v>655634</v>
       </c>
       <c r="R18" t="n">
-        <v>7033064</v>
+        <v>7033016</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2472,6 +2462,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>En hane på födosök</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2502,10 +2497,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113712242</v>
+        <v>113712223</v>
       </c>
       <c r="B19" t="n">
-        <v>90135</v>
+        <v>81944</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2518,21 +2513,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2542,10 +2537,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>655598</v>
+        <v>655214</v>
       </c>
       <c r="R19" t="n">
-        <v>7033035</v>
+        <v>7033129</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2608,10 +2603,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113712237</v>
+        <v>113714470</v>
       </c>
       <c r="B20" t="n">
-        <v>81944</v>
+        <v>97402</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2620,25 +2615,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2648,10 +2643,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>655511</v>
+        <v>655550</v>
       </c>
       <c r="R20" t="n">
-        <v>7033085</v>
+        <v>7033068</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2684,6 +2679,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>60 orkidéer ca</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2714,7 +2714,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113714459</v>
+        <v>113712246</v>
       </c>
       <c r="B21" t="n">
         <v>97402</v>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>655289</v>
+        <v>655686</v>
       </c>
       <c r="R21" t="n">
-        <v>7033162</v>
+        <v>7032933</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2825,10 +2825,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113712235</v>
+        <v>113712252</v>
       </c>
       <c r="B22" t="n">
-        <v>97402</v>
+        <v>90135</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2837,25 +2837,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2865,10 +2865,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>655505</v>
+        <v>655735</v>
       </c>
       <c r="R22" t="n">
-        <v>7033075</v>
+        <v>7032900</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2901,11 +2901,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>200 orkidéer ca</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2936,10 +2931,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113712233</v>
+        <v>113712234</v>
       </c>
       <c r="B23" t="n">
-        <v>90146</v>
+        <v>90135</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2948,25 +2943,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2976,10 +2971,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>655490</v>
+        <v>655508</v>
       </c>
       <c r="R23" t="n">
-        <v>7033070</v>
+        <v>7033069</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3042,10 +3037,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113712243</v>
+        <v>113712214</v>
       </c>
       <c r="B24" t="n">
-        <v>79265</v>
+        <v>90577</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3054,25 +3049,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3082,10 +3077,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>655606</v>
+        <v>655420</v>
       </c>
       <c r="R24" t="n">
-        <v>7033029</v>
+        <v>7032948</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3118,11 +3113,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På 200 åriga björkar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3153,10 +3143,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113714481</v>
+        <v>113712231</v>
       </c>
       <c r="B25" t="n">
-        <v>90146</v>
+        <v>90135</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3165,25 +3155,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3193,10 +3183,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>655742</v>
+        <v>655431</v>
       </c>
       <c r="R25" t="n">
-        <v>7032893</v>
+        <v>7033087</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3259,10 +3249,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113714477</v>
+        <v>113712226</v>
       </c>
       <c r="B26" t="n">
-        <v>97402</v>
+        <v>90577</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3275,21 +3265,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3299,10 +3289,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>655686</v>
+        <v>655210</v>
       </c>
       <c r="R26" t="n">
-        <v>7032933</v>
+        <v>7033162</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3335,11 +3325,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>50 orkidéer ca</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3370,7 +3355,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113712241</v>
+        <v>113714474</v>
       </c>
       <c r="B27" t="n">
         <v>79265</v>
@@ -3410,10 +3395,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>655567</v>
+        <v>655606</v>
       </c>
       <c r="R27" t="n">
-        <v>7033045</v>
+        <v>7033029</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3450,7 +3435,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gamla aspar</t>
+          <t>På 200 åriga björkar</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3481,7 +3466,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113714482</v>
+        <v>113712245</v>
       </c>
       <c r="B28" t="n">
         <v>79265</v>
@@ -3521,10 +3506,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>655742</v>
+        <v>655683</v>
       </c>
       <c r="R28" t="n">
-        <v>7032893</v>
+        <v>7032960</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3561,7 +3546,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På en asphögstubbe</t>
+          <t>På sälghögstube</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3698,7 +3683,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113712252</v>
+        <v>113714480</v>
       </c>
       <c r="B30" t="n">
         <v>90135</v>
@@ -3738,10 +3723,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>655735</v>
+        <v>655709</v>
       </c>
       <c r="R30" t="n">
-        <v>7032900</v>
+        <v>7032901</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3804,10 +3789,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113712222</v>
+        <v>113714479</v>
       </c>
       <c r="B31" t="n">
-        <v>81944</v>
+        <v>90135</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3820,21 +3805,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3844,10 +3829,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>655276</v>
+        <v>655704</v>
       </c>
       <c r="R31" t="n">
-        <v>7033079</v>
+        <v>7032901</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3888,7 +3873,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3911,10 +3895,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113712248</v>
+        <v>113712225</v>
       </c>
       <c r="B32" t="n">
-        <v>90135</v>
+        <v>97402</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3923,25 +3907,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3951,10 +3935,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>655704</v>
+        <v>655214</v>
       </c>
       <c r="R32" t="n">
-        <v>7032901</v>
+        <v>7033152</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3987,6 +3971,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>30 orkidéer</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4017,10 +4006,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113712221</v>
+        <v>113714444</v>
       </c>
       <c r="B33" t="n">
-        <v>56955</v>
+        <v>79265</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4033,21 +4022,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4057,10 +4046,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>655150</v>
+        <v>655471</v>
       </c>
       <c r="R33" t="n">
-        <v>7033208</v>
+        <v>7032880</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4097,7 +4086,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ett par i sitt häckningsrevir och födosöksområde</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4128,10 +4117,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113714456</v>
+        <v>113714448</v>
       </c>
       <c r="B34" t="n">
-        <v>97402</v>
+        <v>78201</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4140,25 +4129,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4168,10 +4157,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>655214</v>
+        <v>655402</v>
       </c>
       <c r="R34" t="n">
-        <v>7033152</v>
+        <v>7033004</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4208,7 +4197,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>30 orkidéer</t>
+          <t>Riklig</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4239,10 +4228,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113712247</v>
+        <v>113714469</v>
       </c>
       <c r="B35" t="n">
-        <v>90416</v>
+        <v>90135</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4255,21 +4244,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4279,10 +4268,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>655697</v>
+        <v>655543</v>
       </c>
       <c r="R35" t="n">
-        <v>7032900</v>
+        <v>7033064</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4345,10 +4334,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113712218</v>
+        <v>113714447</v>
       </c>
       <c r="B36" t="n">
-        <v>90522</v>
+        <v>90135</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4361,16 +4350,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4380,10 +4374,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>655338</v>
+        <v>655408</v>
       </c>
       <c r="R36" t="n">
-        <v>7033023</v>
+        <v>7032957</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4446,10 +4440,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113712211</v>
+        <v>113714461</v>
       </c>
       <c r="B37" t="n">
-        <v>90135</v>
+        <v>90577</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4458,25 +4452,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4486,10 +4480,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>655477</v>
+        <v>655330</v>
       </c>
       <c r="R37" t="n">
-        <v>7032872</v>
+        <v>7033148</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4552,10 +4546,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113714484</v>
+        <v>113714453</v>
       </c>
       <c r="B38" t="n">
-        <v>90522</v>
+        <v>56955</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4568,16 +4562,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6040186</v>
+        <v>103021</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4587,10 +4586,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>655744</v>
+        <v>655150</v>
       </c>
       <c r="R38" t="n">
-        <v>7032871</v>
+        <v>7033208</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4623,6 +4622,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ett par i sitt häckningsrevir och födosöksområde</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4653,10 +4657,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113712234</v>
+        <v>113712253</v>
       </c>
       <c r="B39" t="n">
-        <v>90135</v>
+        <v>90522</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4669,21 +4673,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4693,10 +4692,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>655508</v>
+        <v>655744</v>
       </c>
       <c r="R39" t="n">
-        <v>7033069</v>
+        <v>7032871</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4759,10 +4758,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113714461</v>
+        <v>113712222</v>
       </c>
       <c r="B40" t="n">
-        <v>90577</v>
+        <v>81944</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4771,25 +4770,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1209</v>
+        <v>1312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4799,10 +4798,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>655330</v>
+        <v>655276</v>
       </c>
       <c r="R40" t="n">
-        <v>7033148</v>
+        <v>7033079</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4843,6 +4842,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4865,7 +4865,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113712220</v>
+        <v>113714452</v>
       </c>
       <c r="B41" t="n">
         <v>90081</v>

--- a/artfynd/A 60241-2023 artfynd.xlsx
+++ b/artfynd/A 60241-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113714445</v>
+        <v>113714473</v>
       </c>
       <c r="B2" t="n">
-        <v>90099</v>
+        <v>90135</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655446</v>
+        <v>655598</v>
       </c>
       <c r="R2" t="n">
-        <v>7032922</v>
+        <v>7033035</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113712235</v>
+        <v>113714480</v>
       </c>
       <c r="B3" t="n">
-        <v>97402</v>
+        <v>90135</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655505</v>
+        <v>655709</v>
       </c>
       <c r="R3" t="n">
-        <v>7033075</v>
+        <v>7032901</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,11 +857,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>200 orkidéer ca</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113714450</v>
+        <v>113712221</v>
       </c>
       <c r="B4" t="n">
-        <v>90522</v>
+        <v>56955</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,16 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6040186</v>
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655338</v>
+        <v>655150</v>
       </c>
       <c r="R4" t="n">
-        <v>7033023</v>
+        <v>7033208</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -963,6 +963,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ett par i sitt häckningsrevir och födosöksområde</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113714442</v>
+        <v>113714485</v>
       </c>
       <c r="B5" t="n">
-        <v>90135</v>
+        <v>90153</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1014,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655477</v>
+        <v>655756</v>
       </c>
       <c r="R5" t="n">
-        <v>7032872</v>
+        <v>7032864</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113712237</v>
+        <v>113712250</v>
       </c>
       <c r="B6" t="n">
-        <v>81944</v>
+        <v>90146</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1116,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>1205</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655511</v>
+        <v>655742</v>
       </c>
       <c r="R6" t="n">
-        <v>7033085</v>
+        <v>7032893</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113712241</v>
+        <v>113714448</v>
       </c>
       <c r="B7" t="n">
-        <v>79265</v>
+        <v>78201</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>655567</v>
+        <v>655402</v>
       </c>
       <c r="R7" t="n">
-        <v>7033045</v>
+        <v>7033004</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1285,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gamla aspar</t>
+          <t>Riklig</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113714482</v>
+        <v>113714477</v>
       </c>
       <c r="B8" t="n">
-        <v>79265</v>
+        <v>97402</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,25 +1333,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>655742</v>
+        <v>655686</v>
       </c>
       <c r="R8" t="n">
-        <v>7032893</v>
+        <v>7032933</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1396,7 +1401,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På en asphögstubbe</t>
+          <t>50 orkidéer ca</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,10 +1432,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113712247</v>
+        <v>113712239</v>
       </c>
       <c r="B9" t="n">
-        <v>90416</v>
+        <v>97402</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,25 +1444,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1472,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>655697</v>
+        <v>655550</v>
       </c>
       <c r="R9" t="n">
-        <v>7032900</v>
+        <v>7033068</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1503,6 +1508,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>60 orkidéer ca</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1533,10 +1543,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113712227</v>
+        <v>113714444</v>
       </c>
       <c r="B10" t="n">
-        <v>97402</v>
+        <v>79265</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1545,25 +1555,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1573,10 +1583,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>655289</v>
+        <v>655471</v>
       </c>
       <c r="R10" t="n">
-        <v>7033162</v>
+        <v>7032880</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1613,7 +1623,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>50 orkidéer ca</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1644,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113714465</v>
+        <v>113712252</v>
       </c>
       <c r="B11" t="n">
-        <v>90146</v>
+        <v>90135</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1656,25 +1666,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1684,10 +1694,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>655490</v>
+        <v>655735</v>
       </c>
       <c r="R11" t="n">
-        <v>7033070</v>
+        <v>7032900</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1750,7 +1760,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113714460</v>
+        <v>113712247</v>
       </c>
       <c r="B12" t="n">
         <v>90416</v>
@@ -1790,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>655333</v>
+        <v>655697</v>
       </c>
       <c r="R12" t="n">
-        <v>7033147</v>
+        <v>7032900</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1856,10 +1866,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113714471</v>
+        <v>113714447</v>
       </c>
       <c r="B13" t="n">
-        <v>79223</v>
+        <v>90135</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1868,25 +1878,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1896,10 +1906,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>655561</v>
+        <v>655408</v>
       </c>
       <c r="R13" t="n">
-        <v>7033047</v>
+        <v>7032957</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1962,10 +1972,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113714485</v>
+        <v>113712253</v>
       </c>
       <c r="B14" t="n">
-        <v>90153</v>
+        <v>90522</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1978,21 +1988,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2002,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>655756</v>
+        <v>655744</v>
       </c>
       <c r="R14" t="n">
-        <v>7032864</v>
+        <v>7032871</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2068,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113712217</v>
+        <v>113714446</v>
       </c>
       <c r="B15" t="n">
-        <v>90416</v>
+        <v>90577</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2080,25 +2085,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2108,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>655373</v>
+        <v>655420</v>
       </c>
       <c r="R15" t="n">
-        <v>7033024</v>
+        <v>7032948</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2174,10 +2179,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113712242</v>
+        <v>113714471</v>
       </c>
       <c r="B16" t="n">
-        <v>90135</v>
+        <v>79223</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2186,25 +2191,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2214,10 +2219,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>655598</v>
+        <v>655561</v>
       </c>
       <c r="R16" t="n">
-        <v>7033035</v>
+        <v>7033047</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2280,10 +2285,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113712250</v>
+        <v>113712235</v>
       </c>
       <c r="B17" t="n">
-        <v>90146</v>
+        <v>97402</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2292,25 +2297,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1205</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2320,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655742</v>
+        <v>655505</v>
       </c>
       <c r="R17" t="n">
-        <v>7032893</v>
+        <v>7033075</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2356,6 +2361,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>200 orkidéer ca</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2386,10 +2396,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113714475</v>
+        <v>113714450</v>
       </c>
       <c r="B18" t="n">
-        <v>56826</v>
+        <v>90522</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2402,21 +2412,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2426,10 +2431,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655634</v>
+        <v>655338</v>
       </c>
       <c r="R18" t="n">
-        <v>7033016</v>
+        <v>7033023</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2462,11 +2467,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>En hane på födosök</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2497,10 +2497,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113712223</v>
+        <v>113714463</v>
       </c>
       <c r="B19" t="n">
-        <v>81944</v>
+        <v>90135</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2513,21 +2513,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>655214</v>
+        <v>655431</v>
       </c>
       <c r="R19" t="n">
-        <v>7033129</v>
+        <v>7033087</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2603,10 +2603,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113714470</v>
+        <v>113714474</v>
       </c>
       <c r="B20" t="n">
-        <v>97402</v>
+        <v>79265</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2615,25 +2615,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>655550</v>
+        <v>655606</v>
       </c>
       <c r="R20" t="n">
-        <v>7033068</v>
+        <v>7033029</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>60 orkidéer ca</t>
+          <t>På 200 åriga björkar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2714,10 +2714,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113712246</v>
+        <v>113714449</v>
       </c>
       <c r="B21" t="n">
-        <v>97402</v>
+        <v>90416</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2726,25 +2726,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>655686</v>
+        <v>655373</v>
       </c>
       <c r="R21" t="n">
-        <v>7032933</v>
+        <v>7033024</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2790,11 +2790,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>50 orkidéer ca</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2825,10 +2820,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113712252</v>
+        <v>113714475</v>
       </c>
       <c r="B22" t="n">
-        <v>90135</v>
+        <v>56826</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2841,21 +2836,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2865,10 +2860,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>655735</v>
+        <v>655634</v>
       </c>
       <c r="R22" t="n">
-        <v>7032900</v>
+        <v>7033016</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2901,6 +2896,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>En hane på födosök</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2931,10 +2931,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113712234</v>
+        <v>113712225</v>
       </c>
       <c r="B23" t="n">
-        <v>90135</v>
+        <v>97402</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2943,25 +2943,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>655508</v>
+        <v>655214</v>
       </c>
       <c r="R23" t="n">
-        <v>7033069</v>
+        <v>7033152</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3007,6 +3007,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>30 orkidéer</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3037,10 +3042,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113712214</v>
+        <v>113712219</v>
       </c>
       <c r="B24" t="n">
-        <v>90577</v>
+        <v>90153</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3049,25 +3054,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3077,10 +3082,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>655420</v>
+        <v>655296</v>
       </c>
       <c r="R24" t="n">
-        <v>7032948</v>
+        <v>7033043</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3143,10 +3148,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113712231</v>
+        <v>113714445</v>
       </c>
       <c r="B25" t="n">
-        <v>90135</v>
+        <v>90099</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3155,25 +3160,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3183,10 +3188,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>655431</v>
+        <v>655446</v>
       </c>
       <c r="R25" t="n">
-        <v>7033087</v>
+        <v>7032922</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3249,7 +3254,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113712226</v>
+        <v>113712229</v>
       </c>
       <c r="B26" t="n">
         <v>90577</v>
@@ -3289,10 +3294,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>655210</v>
+        <v>655330</v>
       </c>
       <c r="R26" t="n">
-        <v>7033162</v>
+        <v>7033148</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3355,10 +3360,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113714474</v>
+        <v>113712226</v>
       </c>
       <c r="B27" t="n">
-        <v>79265</v>
+        <v>90577</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3367,25 +3372,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3395,10 +3400,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>655606</v>
+        <v>655210</v>
       </c>
       <c r="R27" t="n">
-        <v>7033029</v>
+        <v>7033162</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3431,11 +3436,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På 200 åriga björkar</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3466,10 +3466,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113712245</v>
+        <v>113714442</v>
       </c>
       <c r="B28" t="n">
-        <v>79265</v>
+        <v>90135</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3482,21 +3482,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3506,10 +3506,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>655683</v>
+        <v>655477</v>
       </c>
       <c r="R28" t="n">
-        <v>7032960</v>
+        <v>7032872</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3542,11 +3542,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På sälghögstube</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3577,10 +3572,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113712219</v>
+        <v>113712241</v>
       </c>
       <c r="B29" t="n">
-        <v>90153</v>
+        <v>79265</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3593,21 +3588,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3617,10 +3612,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>655296</v>
+        <v>655567</v>
       </c>
       <c r="R29" t="n">
-        <v>7033043</v>
+        <v>7033045</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3653,6 +3648,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På gamla aspar</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3683,10 +3683,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113714480</v>
+        <v>113712251</v>
       </c>
       <c r="B30" t="n">
-        <v>90135</v>
+        <v>79265</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3699,21 +3699,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3723,10 +3723,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>655709</v>
+        <v>655742</v>
       </c>
       <c r="R30" t="n">
-        <v>7032901</v>
+        <v>7032893</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3759,6 +3759,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På en asphögstubbe</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3789,10 +3794,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113714479</v>
+        <v>113712233</v>
       </c>
       <c r="B31" t="n">
-        <v>90135</v>
+        <v>90146</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3801,25 +3806,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3829,10 +3834,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>655704</v>
+        <v>655490</v>
       </c>
       <c r="R31" t="n">
-        <v>7032901</v>
+        <v>7033070</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3895,10 +3900,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113712225</v>
+        <v>113712238</v>
       </c>
       <c r="B32" t="n">
-        <v>97402</v>
+        <v>90135</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3907,25 +3912,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3935,10 +3940,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>655214</v>
+        <v>655543</v>
       </c>
       <c r="R32" t="n">
-        <v>7033152</v>
+        <v>7033064</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3971,11 +3976,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>30 orkidéer</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4006,10 +4006,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113714444</v>
+        <v>113714452</v>
       </c>
       <c r="B33" t="n">
-        <v>79265</v>
+        <v>90081</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4022,21 +4022,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4046,10 +4046,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>655471</v>
+        <v>655288</v>
       </c>
       <c r="R33" t="n">
-        <v>7032880</v>
+        <v>7033050</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4082,11 +4082,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4117,10 +4112,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113714448</v>
+        <v>113712245</v>
       </c>
       <c r="B34" t="n">
-        <v>78201</v>
+        <v>79265</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4133,21 +4128,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4157,10 +4152,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>655402</v>
+        <v>655683</v>
       </c>
       <c r="R34" t="n">
-        <v>7033004</v>
+        <v>7032960</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4197,7 +4192,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Riklig</t>
+          <t>På sälghögstube</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4228,10 +4223,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113714469</v>
+        <v>113714455</v>
       </c>
       <c r="B35" t="n">
-        <v>90135</v>
+        <v>81944</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4244,21 +4239,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4268,10 +4263,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>655543</v>
+        <v>655214</v>
       </c>
       <c r="R35" t="n">
-        <v>7033064</v>
+        <v>7033129</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4334,10 +4329,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113714447</v>
+        <v>113714468</v>
       </c>
       <c r="B36" t="n">
-        <v>90135</v>
+        <v>81944</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4350,21 +4345,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4374,10 +4369,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>655408</v>
+        <v>655511</v>
       </c>
       <c r="R36" t="n">
-        <v>7032957</v>
+        <v>7033085</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4440,10 +4435,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113714461</v>
+        <v>113714460</v>
       </c>
       <c r="B37" t="n">
-        <v>90577</v>
+        <v>90416</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4452,25 +4447,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4480,10 +4475,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>655330</v>
+        <v>655333</v>
       </c>
       <c r="R37" t="n">
-        <v>7033148</v>
+        <v>7033147</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4546,10 +4541,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113714453</v>
+        <v>113712222</v>
       </c>
       <c r="B38" t="n">
-        <v>56955</v>
+        <v>81944</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4562,21 +4557,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4586,10 +4581,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>655150</v>
+        <v>655276</v>
       </c>
       <c r="R38" t="n">
-        <v>7033208</v>
+        <v>7033079</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4624,17 +4619,13 @@
           <t>2023-10-15</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ett par i sitt häckningsrevir och födosöksområde</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4657,10 +4648,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113712253</v>
+        <v>113712234</v>
       </c>
       <c r="B39" t="n">
-        <v>90522</v>
+        <v>90135</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4673,16 +4664,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4692,10 +4688,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>655744</v>
+        <v>655508</v>
       </c>
       <c r="R39" t="n">
-        <v>7032871</v>
+        <v>7033069</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4758,10 +4754,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113712222</v>
+        <v>113714479</v>
       </c>
       <c r="B40" t="n">
-        <v>81944</v>
+        <v>90135</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4774,21 +4770,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4798,10 +4794,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>655276</v>
+        <v>655704</v>
       </c>
       <c r="R40" t="n">
-        <v>7033079</v>
+        <v>7032901</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4842,7 +4838,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4865,10 +4860,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113714452</v>
+        <v>113714459</v>
       </c>
       <c r="B41" t="n">
-        <v>90081</v>
+        <v>97402</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4877,25 +4872,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4905,10 +4900,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>655288</v>
+        <v>655289</v>
       </c>
       <c r="R41" t="n">
-        <v>7033050</v>
+        <v>7033162</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4941,6 +4936,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>50 orkidéer ca</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 60241-2023 artfynd.xlsx
+++ b/artfynd/A 60241-2023 artfynd.xlsx
@@ -2073,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113714446</v>
+        <v>113714471</v>
       </c>
       <c r="B15" t="n">
-        <v>90577</v>
+        <v>79223</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2085,25 +2085,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>229497</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>655420</v>
+        <v>655561</v>
       </c>
       <c r="R15" t="n">
-        <v>7032948</v>
+        <v>7033047</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2179,10 +2179,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113714471</v>
+        <v>113714450</v>
       </c>
       <c r="B16" t="n">
-        <v>79223</v>
+        <v>90522</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2191,25 +2191,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229497</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Korallblylav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2219,10 +2214,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>655561</v>
+        <v>655338</v>
       </c>
       <c r="R16" t="n">
-        <v>7033047</v>
+        <v>7033023</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2285,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113712235</v>
+        <v>113714446</v>
       </c>
       <c r="B17" t="n">
-        <v>97402</v>
+        <v>90577</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2301,21 +2296,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2325,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655505</v>
+        <v>655420</v>
       </c>
       <c r="R17" t="n">
-        <v>7033075</v>
+        <v>7032948</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2361,11 +2356,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>200 orkidéer ca</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2396,10 +2386,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113714450</v>
+        <v>113712235</v>
       </c>
       <c r="B18" t="n">
-        <v>90522</v>
+        <v>97402</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2408,20 +2398,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6040186</v>
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2431,10 +2426,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655338</v>
+        <v>655505</v>
       </c>
       <c r="R18" t="n">
-        <v>7033023</v>
+        <v>7033075</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2467,6 +2462,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>200 orkidéer ca</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3683,10 +3683,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113712251</v>
+        <v>113712238</v>
       </c>
       <c r="B30" t="n">
-        <v>79265</v>
+        <v>90135</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3699,21 +3699,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3723,10 +3723,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>655742</v>
+        <v>655543</v>
       </c>
       <c r="R30" t="n">
-        <v>7032893</v>
+        <v>7033064</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3759,11 +3759,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På en asphögstubbe</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3794,10 +3789,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113712233</v>
+        <v>113712251</v>
       </c>
       <c r="B31" t="n">
-        <v>90146</v>
+        <v>79265</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3806,25 +3801,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3834,10 +3829,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>655490</v>
+        <v>655742</v>
       </c>
       <c r="R31" t="n">
-        <v>7033070</v>
+        <v>7032893</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3870,6 +3865,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På en asphögstubbe</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3900,10 +3900,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113712238</v>
+        <v>113712233</v>
       </c>
       <c r="B32" t="n">
-        <v>90135</v>
+        <v>90146</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3912,25 +3912,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3940,10 +3940,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>655543</v>
+        <v>655490</v>
       </c>
       <c r="R32" t="n">
-        <v>7033064</v>
+        <v>7033070</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4648,10 +4648,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113712234</v>
+        <v>113714459</v>
       </c>
       <c r="B39" t="n">
-        <v>90135</v>
+        <v>97402</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4660,25 +4660,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4688,10 +4688,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>655508</v>
+        <v>655289</v>
       </c>
       <c r="R39" t="n">
-        <v>7033069</v>
+        <v>7033162</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4724,6 +4724,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>50 orkidéer ca</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4754,7 +4759,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113714479</v>
+        <v>113712234</v>
       </c>
       <c r="B40" t="n">
         <v>90135</v>
@@ -4794,10 +4799,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>655704</v>
+        <v>655508</v>
       </c>
       <c r="R40" t="n">
-        <v>7032901</v>
+        <v>7033069</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4860,10 +4865,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113714459</v>
+        <v>113714479</v>
       </c>
       <c r="B41" t="n">
-        <v>97402</v>
+        <v>90135</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4872,25 +4877,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4900,10 +4905,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>655289</v>
+        <v>655704</v>
       </c>
       <c r="R41" t="n">
-        <v>7033162</v>
+        <v>7032901</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4936,11 +4941,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>50 orkidéer ca</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 60241-2023 artfynd.xlsx
+++ b/artfynd/A 60241-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113714473</v>
+        <v>113712222</v>
       </c>
       <c r="B2" t="n">
-        <v>90135</v>
+        <v>81944</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655598</v>
+        <v>655276</v>
       </c>
       <c r="R2" t="n">
-        <v>7033035</v>
+        <v>7033079</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,6 +759,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113714480</v>
+        <v>113712237</v>
       </c>
       <c r="B3" t="n">
-        <v>90135</v>
+        <v>81944</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655709</v>
+        <v>655511</v>
       </c>
       <c r="R3" t="n">
-        <v>7032901</v>
+        <v>7033085</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113712221</v>
+        <v>113714475</v>
       </c>
       <c r="B4" t="n">
-        <v>56955</v>
+        <v>56826</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655150</v>
+        <v>655634</v>
       </c>
       <c r="R4" t="n">
-        <v>7033208</v>
+        <v>7033016</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -967,7 +968,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ett par i sitt häckningsrevir och födosöksområde</t>
+          <t>En hane på födosök</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113714485</v>
+        <v>113712242</v>
       </c>
       <c r="B5" t="n">
-        <v>90153</v>
+        <v>90135</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,21 +1015,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655756</v>
+        <v>655598</v>
       </c>
       <c r="R5" t="n">
-        <v>7032864</v>
+        <v>7033035</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113712250</v>
+        <v>113714478</v>
       </c>
       <c r="B6" t="n">
-        <v>90146</v>
+        <v>90416</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,25 +1117,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1205</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1145,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655742</v>
+        <v>655697</v>
       </c>
       <c r="R6" t="n">
-        <v>7032893</v>
+        <v>7032900</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1210,10 +1211,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113714448</v>
+        <v>113712252</v>
       </c>
       <c r="B7" t="n">
-        <v>78201</v>
+        <v>90135</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1227,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>655402</v>
+        <v>655735</v>
       </c>
       <c r="R7" t="n">
-        <v>7033004</v>
+        <v>7032900</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1286,11 +1287,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Riklig</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113714477</v>
+        <v>113712226</v>
       </c>
       <c r="B8" t="n">
-        <v>97402</v>
+        <v>90577</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>655686</v>
+        <v>655210</v>
       </c>
       <c r="R8" t="n">
-        <v>7032933</v>
+        <v>7033162</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1397,11 +1393,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>50 orkidéer ca</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,7 +1423,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113712239</v>
+        <v>113712225</v>
       </c>
       <c r="B9" t="n">
         <v>97402</v>
@@ -1472,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>655550</v>
+        <v>655214</v>
       </c>
       <c r="R9" t="n">
-        <v>7033068</v>
+        <v>7033152</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1512,7 +1503,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>60 orkidéer ca</t>
+          <t>30 orkidéer</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1543,10 +1534,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113714444</v>
+        <v>113712235</v>
       </c>
       <c r="B10" t="n">
-        <v>79265</v>
+        <v>97402</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1555,25 +1546,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1583,10 +1574,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>655471</v>
+        <v>655505</v>
       </c>
       <c r="R10" t="n">
-        <v>7032880</v>
+        <v>7033075</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1623,7 +1614,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>200 orkidéer ca</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1654,10 +1645,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113712252</v>
+        <v>113714477</v>
       </c>
       <c r="B11" t="n">
-        <v>90135</v>
+        <v>97402</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1666,25 +1657,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1694,10 +1685,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>655735</v>
+        <v>655686</v>
       </c>
       <c r="R11" t="n">
-        <v>7032900</v>
+        <v>7032933</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1730,6 +1721,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>50 orkidéer ca</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,10 +1756,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113712247</v>
+        <v>113712254</v>
       </c>
       <c r="B12" t="n">
-        <v>90416</v>
+        <v>90153</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1776,21 +1772,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1800,10 +1796,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>655697</v>
+        <v>655756</v>
       </c>
       <c r="R12" t="n">
-        <v>7032900</v>
+        <v>7032864</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1866,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113714447</v>
+        <v>113714446</v>
       </c>
       <c r="B13" t="n">
-        <v>90135</v>
+        <v>90577</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1878,25 +1874,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1906,10 +1902,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>655408</v>
+        <v>655420</v>
       </c>
       <c r="R13" t="n">
-        <v>7032957</v>
+        <v>7032948</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1972,10 +1968,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113712253</v>
+        <v>113712233</v>
       </c>
       <c r="B14" t="n">
-        <v>90522</v>
+        <v>90146</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1984,20 +1980,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6040186</v>
+        <v>1205</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Stor aspticka</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2007,10 +2008,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>655744</v>
+        <v>655490</v>
       </c>
       <c r="R14" t="n">
-        <v>7032871</v>
+        <v>7033070</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2073,10 +2074,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113714471</v>
+        <v>113714469</v>
       </c>
       <c r="B15" t="n">
-        <v>79223</v>
+        <v>90135</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2085,25 +2086,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2113,10 +2114,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>655561</v>
+        <v>655543</v>
       </c>
       <c r="R15" t="n">
-        <v>7033047</v>
+        <v>7033064</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2179,10 +2180,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113714450</v>
+        <v>113712243</v>
       </c>
       <c r="B16" t="n">
-        <v>90522</v>
+        <v>79265</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2195,16 +2196,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6040186</v>
+        <v>6458</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2214,10 +2220,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>655338</v>
+        <v>655606</v>
       </c>
       <c r="R16" t="n">
-        <v>7033023</v>
+        <v>7033029</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2250,6 +2256,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På 200 åriga björkar</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,10 +2291,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113714446</v>
+        <v>113712227</v>
       </c>
       <c r="B17" t="n">
-        <v>90577</v>
+        <v>97402</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2296,21 +2307,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2320,10 +2331,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655420</v>
+        <v>655289</v>
       </c>
       <c r="R17" t="n">
-        <v>7032948</v>
+        <v>7033162</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2356,6 +2367,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>50 orkidéer ca</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2386,10 +2402,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113712235</v>
+        <v>113712220</v>
       </c>
       <c r="B18" t="n">
-        <v>97402</v>
+        <v>90081</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2398,25 +2414,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2426,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655505</v>
+        <v>655288</v>
       </c>
       <c r="R18" t="n">
-        <v>7033075</v>
+        <v>7033050</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2462,11 +2478,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>200 orkidéer ca</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2497,10 +2508,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113714463</v>
+        <v>113712216</v>
       </c>
       <c r="B19" t="n">
-        <v>90135</v>
+        <v>78201</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2513,21 +2524,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2537,10 +2548,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>655431</v>
+        <v>655402</v>
       </c>
       <c r="R19" t="n">
-        <v>7033087</v>
+        <v>7033004</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2573,6 +2584,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Riklig</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2603,7 +2619,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113714474</v>
+        <v>113712251</v>
       </c>
       <c r="B20" t="n">
         <v>79265</v>
@@ -2643,10 +2659,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>655606</v>
+        <v>655742</v>
       </c>
       <c r="R20" t="n">
-        <v>7033029</v>
+        <v>7032893</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2683,7 +2699,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På 200 åriga björkar</t>
+          <t>På en asphögstubbe</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2714,10 +2730,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113714449</v>
+        <v>113714453</v>
       </c>
       <c r="B21" t="n">
-        <v>90416</v>
+        <v>56955</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2730,21 +2746,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2754,10 +2770,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>655373</v>
+        <v>655150</v>
       </c>
       <c r="R21" t="n">
-        <v>7033024</v>
+        <v>7033208</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2790,6 +2806,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ett par i sitt häckningsrevir och födosöksområde</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2820,10 +2841,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113714475</v>
+        <v>113712253</v>
       </c>
       <c r="B22" t="n">
-        <v>56826</v>
+        <v>90522</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2836,21 +2857,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2860,10 +2876,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>655634</v>
+        <v>655744</v>
       </c>
       <c r="R22" t="n">
-        <v>7033016</v>
+        <v>7032871</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2896,11 +2912,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>En hane på födosök</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2931,10 +2942,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113712225</v>
+        <v>113712234</v>
       </c>
       <c r="B23" t="n">
-        <v>97402</v>
+        <v>90135</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2943,25 +2954,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2971,10 +2982,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>655214</v>
+        <v>655508</v>
       </c>
       <c r="R23" t="n">
-        <v>7033152</v>
+        <v>7033069</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3007,11 +3018,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>30 orkidéer</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3042,10 +3048,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113712219</v>
+        <v>113712212</v>
       </c>
       <c r="B24" t="n">
-        <v>90153</v>
+        <v>79265</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3058,21 +3064,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3082,10 +3088,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>655296</v>
+        <v>655471</v>
       </c>
       <c r="R24" t="n">
-        <v>7033043</v>
+        <v>7032880</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3118,6 +3124,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3148,10 +3159,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113714445</v>
+        <v>113714460</v>
       </c>
       <c r="B25" t="n">
-        <v>90099</v>
+        <v>90416</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3160,25 +3171,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3188,10 +3199,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>655446</v>
+        <v>655333</v>
       </c>
       <c r="R25" t="n">
-        <v>7032922</v>
+        <v>7033147</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3254,10 +3265,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113712229</v>
+        <v>113714451</v>
       </c>
       <c r="B26" t="n">
-        <v>90577</v>
+        <v>90153</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3266,25 +3277,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3294,10 +3305,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>655330</v>
+        <v>655296</v>
       </c>
       <c r="R26" t="n">
-        <v>7033148</v>
+        <v>7033043</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3360,10 +3371,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113712226</v>
+        <v>113712217</v>
       </c>
       <c r="B27" t="n">
-        <v>90577</v>
+        <v>90416</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3372,25 +3383,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3400,10 +3411,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>655210</v>
+        <v>655373</v>
       </c>
       <c r="R27" t="n">
-        <v>7033162</v>
+        <v>7033024</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3466,7 +3477,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113714442</v>
+        <v>113714480</v>
       </c>
       <c r="B28" t="n">
         <v>90135</v>
@@ -3506,10 +3517,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>655477</v>
+        <v>655709</v>
       </c>
       <c r="R28" t="n">
-        <v>7032872</v>
+        <v>7032901</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3572,10 +3583,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113712241</v>
+        <v>113714481</v>
       </c>
       <c r="B29" t="n">
-        <v>79265</v>
+        <v>90146</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3584,25 +3595,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3612,10 +3623,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>655567</v>
+        <v>655742</v>
       </c>
       <c r="R29" t="n">
-        <v>7033045</v>
+        <v>7032893</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3648,11 +3659,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På gamla aspar</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3683,10 +3689,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113712238</v>
+        <v>113712223</v>
       </c>
       <c r="B30" t="n">
-        <v>90135</v>
+        <v>81944</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3699,21 +3705,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3723,10 +3729,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>655543</v>
+        <v>655214</v>
       </c>
       <c r="R30" t="n">
-        <v>7033064</v>
+        <v>7033129</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3789,7 +3795,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113712251</v>
+        <v>113712245</v>
       </c>
       <c r="B31" t="n">
         <v>79265</v>
@@ -3829,10 +3835,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>655742</v>
+        <v>655683</v>
       </c>
       <c r="R31" t="n">
-        <v>7032893</v>
+        <v>7032960</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3869,7 +3875,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På en asphögstubbe</t>
+          <t>På sälghögstube</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3900,10 +3906,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113712233</v>
+        <v>113712229</v>
       </c>
       <c r="B32" t="n">
-        <v>90146</v>
+        <v>90577</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3912,25 +3918,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1205</v>
+        <v>1209</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3940,10 +3946,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>655490</v>
+        <v>655330</v>
       </c>
       <c r="R32" t="n">
-        <v>7033070</v>
+        <v>7033148</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4006,10 +4012,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113714452</v>
+        <v>113714463</v>
       </c>
       <c r="B33" t="n">
-        <v>90081</v>
+        <v>90135</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4022,21 +4028,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4046,10 +4052,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>655288</v>
+        <v>655431</v>
       </c>
       <c r="R33" t="n">
-        <v>7033050</v>
+        <v>7033087</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4112,10 +4118,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113712245</v>
+        <v>113714471</v>
       </c>
       <c r="B34" t="n">
-        <v>79265</v>
+        <v>79223</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4124,25 +4130,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4152,10 +4158,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>655683</v>
+        <v>655561</v>
       </c>
       <c r="R34" t="n">
-        <v>7032960</v>
+        <v>7033047</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4188,11 +4194,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På sälghögstube</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4223,10 +4224,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113714455</v>
+        <v>113714470</v>
       </c>
       <c r="B35" t="n">
-        <v>81944</v>
+        <v>97402</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4235,25 +4236,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4263,10 +4264,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>655214</v>
+        <v>655550</v>
       </c>
       <c r="R35" t="n">
-        <v>7033129</v>
+        <v>7033068</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4299,6 +4300,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>60 orkidéer ca</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4329,10 +4335,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113714468</v>
+        <v>113712213</v>
       </c>
       <c r="B36" t="n">
-        <v>81944</v>
+        <v>90099</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4341,25 +4347,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4369,10 +4375,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>655511</v>
+        <v>655446</v>
       </c>
       <c r="R36" t="n">
-        <v>7033085</v>
+        <v>7032922</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4435,10 +4441,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113714460</v>
+        <v>113714479</v>
       </c>
       <c r="B37" t="n">
-        <v>90416</v>
+        <v>90135</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4451,21 +4457,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4475,10 +4481,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>655333</v>
+        <v>655704</v>
       </c>
       <c r="R37" t="n">
-        <v>7033147</v>
+        <v>7032901</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4541,10 +4547,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113712222</v>
+        <v>113714450</v>
       </c>
       <c r="B38" t="n">
-        <v>81944</v>
+        <v>90522</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4557,21 +4563,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4581,10 +4582,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>655276</v>
+        <v>655338</v>
       </c>
       <c r="R38" t="n">
-        <v>7033079</v>
+        <v>7033023</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4625,7 +4626,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4648,10 +4648,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113714459</v>
+        <v>113712215</v>
       </c>
       <c r="B39" t="n">
-        <v>97402</v>
+        <v>90135</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4660,25 +4660,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4688,10 +4688,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>655289</v>
+        <v>655408</v>
       </c>
       <c r="R39" t="n">
-        <v>7033162</v>
+        <v>7032957</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4724,11 +4724,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2023-10-15</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>50 orkidéer ca</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4759,10 +4754,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113712234</v>
+        <v>113714472</v>
       </c>
       <c r="B40" t="n">
-        <v>90135</v>
+        <v>79265</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4775,21 +4770,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4799,10 +4794,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>655508</v>
+        <v>655567</v>
       </c>
       <c r="R40" t="n">
-        <v>7033069</v>
+        <v>7033045</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4835,6 +4830,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På gamla aspar</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4865,7 +4865,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113714479</v>
+        <v>113712211</v>
       </c>
       <c r="B41" t="n">
         <v>90135</v>
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>655704</v>
+        <v>655477</v>
       </c>
       <c r="R41" t="n">
-        <v>7032901</v>
+        <v>7032872</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>

--- a/artfynd/A 60241-2023 artfynd.xlsx
+++ b/artfynd/A 60241-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
